--- a/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
+++ b/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="165" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89BEC3BE-38F5-4F58-898E-91A1DEA2C4F5}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B0FE64-B59A-486A-993A-6F7758CDCA2D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ManagersRepository" sheetId="1" r:id="rId1"/>
     <sheet name="MajorsRepository" sheetId="2" r:id="rId2"/>
+    <sheet name="SubjectsRepository" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -643,6 +644,459 @@
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
               <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F04EFB40-7736-46DC-97E7-5B003CB43810}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4686300" y="2152650"/>
+          <a:ext cx="2733675" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>extistsByName( name : String )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r Boolean</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72C66C79-68C5-4965-88E5-D067FEF7326A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="13535025" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectsRepository extends JpaRepository&lt;Subject, Integer&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A30D883-42C8-4E7C-9EA3-FA1AF6B4C1E3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{72C66C79-68C5-4965-88E5-D067FEF7326A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1666875" y="2143125"/>
+          <a:ext cx="2733675" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>findByName( name : String )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r Optional&lt;Subject&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44E1E4CD-AD11-4CA9-A5F0-58EC57EBD754}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7A30D883-42C8-4E7C-9EA3-FA1AF6B4C1E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1165,4 +1619,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF6DE0B9-FB1C-46DE-ACC8-1A4FF22CE747}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
+++ b/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B0FE64-B59A-486A-993A-6F7758CDCA2D}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5994428-3281-4639-A205-4C2D109C3D27}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ManagersRepository" sheetId="1" r:id="rId1"/>
     <sheet name="MajorsRepository" sheetId="2" r:id="rId2"/>
     <sheet name="SubjectsRepository" sheetId="3" r:id="rId3"/>
+    <sheet name="ClassesRepository" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1254,6 +1255,89 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>-r Boolean</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811A56CC-40F6-4BB7-A304-D30753BCEA49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassesRepository extends JpaRepository&lt;Major, Integer&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1629,4 +1713,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907DA32A-2360-4BF9-A3D0-A8EF113E6D4E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
+++ b/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5994428-3281-4639-A205-4C2D109C3D27}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62D47CA-3C2D-4A84-A874-2BA01E1C211B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ManagersRepository" sheetId="1" r:id="rId1"/>
@@ -1338,6 +1338,191 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>ClassesRepository extends JpaRepository&lt;Major, Integer&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43AFF5D7-8987-4C2B-85AE-D8808F2928EC}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{811A56CC-40F6-4BB7-A304-D30753BCEA49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1028700" y="2438400"/>
+          <a:ext cx="5838825" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>findByStartYear(  startYear :   Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r List&lt;ClassEntity&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>

--- a/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
+++ b/class_diagram/repository/成績管理sys_クラス図_repository.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="183" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62D47CA-3C2D-4A84-A874-2BA01E1C211B}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D08D1AB8-A237-4E45-9C2E-B6DFE02F4FE3}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,8 @@
     <sheet name="ManagersRepository" sheetId="1" r:id="rId1"/>
     <sheet name="MajorsRepository" sheetId="2" r:id="rId2"/>
     <sheet name="SubjectsRepository" sheetId="3" r:id="rId3"/>
-    <sheet name="ClassesRepository" sheetId="4" r:id="rId4"/>
+    <sheet name="ClassSubjectsRepository" sheetId="5" r:id="rId4"/>
+    <sheet name="ClassesRepository" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1265,6 +1266,89 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B606E4E-5600-4C38-9ACE-57D9B7825586}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSubjectsRepository extends JpaRepository&lt;ClassSubject, Integer&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1901,6 +1985,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D617A92-9D87-4995-A88D-BAE397265193}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907DA32A-2360-4BF9-A3D0-A8EF113E6D4E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
